--- a/PAMF_DIG F2 - monthly2026-07-25.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-25.xlsx
@@ -11656,7 +11656,7 @@
         <v>0.09</v>
       </c>
       <c r="N154" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>0.09</v>
       </c>
       <c r="N203" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
@@ -16474,7 +16474,7 @@
         <v>0.09</v>
       </c>
       <c r="N220" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O220" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>0.09</v>
       </c>
       <c r="N278" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O278" t="inlineStr">
         <is>

--- a/PAMF_DIG F2 - monthly2026-07-25.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-25.xlsx
@@ -1071,7 +1071,7 @@
         <v>0.09</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>0.09</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>0.09</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>0.09</v>
       </c>
       <c r="N31" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>0.09</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>0.09</v>
       </c>
       <c r="N50" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>0.09</v>
       </c>
       <c r="N51" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>0.09</v>
       </c>
       <c r="N64" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>0.09</v>
       </c>
       <c r="N71" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>0.09</v>
       </c>
       <c r="N83" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>0.09</v>
       </c>
       <c r="N87" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>0.09</v>
       </c>
       <c r="N90" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>0.09</v>
       </c>
       <c r="N96" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>0.09</v>
       </c>
       <c r="N109" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>0.09</v>
       </c>
       <c r="N134" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>0.09</v>
       </c>
       <c r="N141" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>0.09</v>
       </c>
       <c r="N144" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>0.09</v>
       </c>
       <c r="N156" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>0.09</v>
       </c>
       <c r="N162" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>0.09</v>
       </c>
       <c r="N166" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>0.09</v>
       </c>
       <c r="N170" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>0.09</v>
       </c>
       <c r="N171" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
         <v>0.09</v>
       </c>
       <c r="N180" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>0.09</v>
       </c>
       <c r="N186" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O186" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>0.09</v>
       </c>
       <c r="N192" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O192" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>0.09</v>
       </c>
       <c r="N200" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>0.09</v>
       </c>
       <c r="N202" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O202" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>0.09</v>
       </c>
       <c r="N207" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O207" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>0.09</v>
       </c>
       <c r="N222" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>0.09</v>
       </c>
       <c r="N229" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>0.09</v>
       </c>
       <c r="N251" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O251" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>0.09</v>
       </c>
       <c r="N271" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O271" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>0.09</v>
       </c>
       <c r="N279" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O279" t="inlineStr">
         <is>
